--- a/data.mn/public/datasets/mrpam-budget-revenue.xlsx
+++ b/data.mn/public/datasets/mrpam-budget-revenue.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,15 +424,14 @@
           <t>Month</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="B1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -440,9 +439,12 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>16685.8</v>
+      </c>
+      <c r="C2" t="n">
         <v>5564.8</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>42230</v>
       </c>
     </row>
@@ -451,9 +453,12 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>36582.5</v>
+      </c>
+      <c r="C3" t="n">
         <v>14840.7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>64607.3</v>
       </c>
     </row>
@@ -462,9 +467,12 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
+        <v>57177.5</v>
+      </c>
+      <c r="C4" t="n">
         <v>22383.8</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>87232.7</v>
       </c>
     </row>
@@ -473,9 +481,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>84426.39999999999</v>
+      </c>
+      <c r="C5" t="n">
         <v>26276.3</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>94912.8</v>
       </c>
     </row>
@@ -484,9 +495,12 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
+        <v>108155.2</v>
+      </c>
+      <c r="C6" t="n">
         <v>31496.3</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>122208.3</v>
       </c>
     </row>
@@ -495,9 +509,12 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
+        <v>137933.8</v>
+      </c>
+      <c r="C7" t="n">
         <v>34696</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>212056</v>
       </c>
     </row>
@@ -506,9 +523,12 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
+        <v>164859.1</v>
+      </c>
+      <c r="C8" t="n">
         <v>38484.2</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>243638.2</v>
       </c>
     </row>
@@ -517,9 +537,12 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
+        <v>191255.3</v>
+      </c>
+      <c r="C9" t="n">
         <v>78426.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>282696.6</v>
       </c>
     </row>
@@ -528,9 +551,12 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>221006.8</v>
+      </c>
+      <c r="C10" t="n">
         <v>118056.5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>305051.2</v>
       </c>
     </row>
@@ -539,9 +565,12 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
+        <v>228926.6</v>
+      </c>
+      <c r="C11" t="n">
         <v>153134.8</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>326666.8</v>
       </c>
     </row>
@@ -550,9 +579,12 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
+        <v>248066.2</v>
+      </c>
+      <c r="C12" t="n">
         <v>182144.3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>345286.4</v>
       </c>
     </row>
@@ -561,9 +593,12 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
+        <v>268696.5</v>
+      </c>
+      <c r="C13" t="n">
         <v>216745.2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>422604.5</v>
       </c>
     </row>
@@ -578,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,7 +645,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -621,15 +656,15 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E2" t="n">
-        <v>5564.8</v>
+        <v>16685.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -640,15 +675,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>2432.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -659,15 +694,15 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E4" t="n">
-        <v>72.59999999999999</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -678,13 +713,15 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>277500</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>183200</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14014.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -695,15 +732,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E6" t="n">
-        <v>200.8</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -714,15 +751,15 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E7" t="n">
-        <v>2479.5</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -733,15 +770,15 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E8" t="n">
-        <v>14840.7</v>
+        <v>36582.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -752,15 +789,15 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E9" t="n">
-        <v>4354.5</v>
+        <v>3637.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="n">
         <v>2</v>
@@ -771,15 +808,15 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E10" t="n">
-        <v>93.40000000000001</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
@@ -790,13 +827,15 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>277500</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>183200</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30860</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
@@ -807,15 +846,15 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E12" t="n">
-        <v>1571.3</v>
+        <v>1034.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
@@ -826,15 +865,15 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E13" t="n">
-        <v>8821.5</v>
+        <v>863.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -845,15 +884,15 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E14" t="n">
-        <v>22383.8</v>
+        <v>57177.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
@@ -864,15 +903,15 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E15" t="n">
-        <v>5962</v>
+        <v>5622.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
@@ -883,15 +922,15 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E16" t="n">
-        <v>197</v>
+        <v>247.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
@@ -902,15 +941,15 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>277500</v>
+        <v>183200</v>
       </c>
       <c r="E17" t="n">
-        <v>861.3</v>
+        <v>46592.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
@@ -921,15 +960,15 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E18" t="n">
-        <v>1721.4</v>
+        <v>1197.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
@@ -940,15 +979,15 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E19" t="n">
-        <v>13642.2</v>
+        <v>3518.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
@@ -959,15 +998,15 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E20" t="n">
-        <v>26276.3</v>
+        <v>84426.39999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
@@ -978,15 +1017,15 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E21" t="n">
-        <v>8138.3</v>
+        <v>7243.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
@@ -997,15 +1036,15 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E22" t="n">
-        <v>246.6</v>
+        <v>284.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
@@ -1016,15 +1055,15 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>277500</v>
+        <v>183200</v>
       </c>
       <c r="E23" t="n">
-        <v>1774.9</v>
+        <v>65710.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
@@ -1035,15 +1074,15 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E24" t="n">
-        <v>1973.4</v>
+        <v>1377.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
@@ -1054,15 +1093,15 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E25" t="n">
-        <v>14143.2</v>
+        <v>9811.200000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B26" t="n">
         <v>5</v>
@@ -1073,15 +1112,15 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E26" t="n">
-        <v>31496.3</v>
+        <v>108155.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
@@ -1092,15 +1131,15 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E27" t="n">
-        <v>12518.9</v>
+        <v>10498.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
@@ -1111,15 +1150,15 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E28" t="n">
-        <v>511.5</v>
+        <v>306.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
@@ -1130,15 +1169,15 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E29" t="n">
-        <v>1774.9</v>
+        <v>85920</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
@@ -1149,15 +1188,15 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E30" t="n">
-        <v>2547.9</v>
+        <v>1619.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
@@ -1168,15 +1207,15 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E31" t="n">
-        <v>14143.2</v>
+        <v>9811.200000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B32" t="n">
         <v>6</v>
@@ -1187,15 +1226,15 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E32" t="n">
-        <v>34696</v>
+        <v>137933.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B33" t="n">
         <v>6</v>
@@ -1206,15 +1245,15 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E33" t="n">
-        <v>15126.7</v>
+        <v>14591.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B34" t="n">
         <v>6</v>
@@ -1225,15 +1264,15 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E34" t="n">
-        <v>620.6</v>
+        <v>415.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B35" t="n">
         <v>6</v>
@@ -1244,15 +1283,15 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E35" t="n">
-        <v>1774.9</v>
+        <v>104956.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B36" t="n">
         <v>6</v>
@@ -1263,15 +1302,15 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E36" t="n">
-        <v>2630.9</v>
+        <v>1771.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B37" t="n">
         <v>6</v>
@@ -1282,15 +1321,15 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E37" t="n">
-        <v>14543</v>
+        <v>16198.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B38" t="n">
         <v>7</v>
@@ -1301,15 +1340,15 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E38" t="n">
-        <v>38484.2</v>
+        <v>164859.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B39" t="n">
         <v>7</v>
@@ -1320,15 +1359,15 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E39" t="n">
-        <v>18776.7</v>
+        <v>16609.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B40" t="n">
         <v>7</v>
@@ -1339,15 +1378,15 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E40" t="n">
-        <v>694.4</v>
+        <v>572.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B41" t="n">
         <v>7</v>
@@ -1358,15 +1397,15 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E41" t="n">
-        <v>1774.9</v>
+        <v>124837.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B42" t="n">
         <v>7</v>
@@ -1377,15 +1416,15 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E42" t="n">
-        <v>2695.2</v>
+        <v>2171.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B43" t="n">
         <v>7</v>
@@ -1396,15 +1435,15 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E43" t="n">
-        <v>14543</v>
+        <v>20668.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B44" t="n">
         <v>8</v>
@@ -1415,15 +1454,15 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E44" t="n">
-        <v>78426.7</v>
+        <v>191255.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B45" t="n">
         <v>8</v>
@@ -1434,15 +1473,15 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E45" t="n">
-        <v>24263</v>
+        <v>21870.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B46" t="n">
         <v>8</v>
@@ -1453,15 +1492,15 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E46" t="n">
-        <v>718.8</v>
+        <v>824.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B47" t="n">
         <v>8</v>
@@ -1472,15 +1511,15 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E47" t="n">
-        <v>36161.3</v>
+        <v>143767.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B48" t="n">
         <v>8</v>
@@ -1491,15 +1530,15 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E48" t="n">
-        <v>2740.5</v>
+        <v>2535.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B49" t="n">
         <v>8</v>
@@ -1510,15 +1549,15 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E49" t="n">
-        <v>14543</v>
+        <v>22256.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B50" t="n">
         <v>9</v>
@@ -1529,15 +1568,15 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E50" t="n">
-        <v>118056.5</v>
+        <v>221006.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B51" t="n">
         <v>9</v>
@@ -1548,15 +1587,15 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E51" t="n">
-        <v>27069.4</v>
+        <v>24526.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B52" t="n">
         <v>9</v>
@@ -1567,15 +1606,15 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E52" t="n">
-        <v>1065.7</v>
+        <v>3153.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B53" t="n">
         <v>9</v>
@@ -1586,15 +1625,15 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E53" t="n">
-        <v>72448.7</v>
+        <v>161552.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B54" t="n">
         <v>9</v>
@@ -1605,15 +1644,15 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E54" t="n">
-        <v>2929.6</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B55" t="n">
         <v>9</v>
@@ -1624,15 +1663,15 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E55" t="n">
-        <v>14543</v>
+        <v>29014.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B56" t="n">
         <v>10</v>
@@ -1643,15 +1682,15 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E56" t="n">
-        <v>153134.8</v>
+        <v>228926.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B57" t="n">
         <v>10</v>
@@ -1662,15 +1701,15 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E57" t="n">
-        <v>30329.5</v>
+        <v>27925.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B58" t="n">
         <v>10</v>
@@ -1681,15 +1720,15 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E58" t="n">
-        <v>1268.2</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B59" t="n">
         <v>10</v>
@@ -1700,15 +1739,15 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E59" t="n">
-        <v>103737.3</v>
+        <v>164612.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B60" t="n">
         <v>10</v>
@@ -1719,15 +1758,15 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E60" t="n">
-        <v>3256.7</v>
+        <v>3567.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B61" t="n">
         <v>10</v>
@@ -1738,15 +1777,15 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E61" t="n">
-        <v>14543</v>
+        <v>29466.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B62" t="n">
         <v>11</v>
@@ -1757,15 +1796,15 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E62" t="n">
-        <v>182144.3</v>
+        <v>248066.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B63" t="n">
         <v>11</v>
@@ -1776,15 +1815,15 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E63" t="n">
-        <v>32862.9</v>
+        <v>30795.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B64" t="n">
         <v>11</v>
@@ -1795,15 +1834,15 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E64" t="n">
-        <v>1497.9</v>
+        <v>3534.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B65" t="n">
         <v>11</v>
@@ -1814,15 +1853,15 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E65" t="n">
-        <v>129688.6</v>
+        <v>180419.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B66" t="n">
         <v>11</v>
@@ -1833,15 +1872,15 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E66" t="n">
-        <v>3552</v>
+        <v>3693.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B67" t="n">
         <v>11</v>
@@ -1852,15 +1891,15 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E67" t="n">
-        <v>14543</v>
+        <v>29623.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B68" t="n">
         <v>12</v>
@@ -1871,15 +1910,15 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E68" t="n">
-        <v>216745.2</v>
+        <v>268696.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B69" t="n">
         <v>12</v>
@@ -1890,15 +1929,15 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E69" t="n">
-        <v>35598.5</v>
+        <v>32770.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B70" t="n">
         <v>12</v>
@@ -1909,15 +1948,15 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E70" t="n">
-        <v>1966.8</v>
+        <v>4409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B71" t="n">
         <v>12</v>
@@ -1928,15 +1967,15 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E71" t="n">
-        <v>160996.1</v>
+        <v>198145.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B72" t="n">
         <v>12</v>
@@ -1947,15 +1986,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E72" t="n">
-        <v>3640.8</v>
+        <v>3748.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B73" t="n">
         <v>12</v>
@@ -1966,15 +2005,15 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E73" t="n">
-        <v>14543</v>
+        <v>29623.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B74" t="n">
         <v>1</v>
@@ -1985,15 +2024,15 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E74" t="n">
-        <v>42230</v>
+        <v>5564.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B75" t="n">
         <v>1</v>
@@ -2004,15 +2043,15 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E75" t="n">
-        <v>3201.7</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B76" t="n">
         <v>1</v>
@@ -2023,15 +2062,15 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E76" t="n">
-        <v>98.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B77" t="n">
         <v>1</v>
@@ -2042,15 +2081,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>347906.1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>38118.7</v>
-      </c>
+        <v>277500</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B78" t="n">
         <v>1</v>
@@ -2061,15 +2098,15 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E78" t="n">
-        <v>811.5</v>
+        <v>200.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B79" t="n">
         <v>1</v>
@@ -2083,12 +2120,12 @@
         <v>25000</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>2479.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B80" t="n">
         <v>2</v>
@@ -2099,15 +2136,15 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E80" t="n">
-        <v>64607.3</v>
+        <v>14840.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B81" t="n">
         <v>2</v>
@@ -2118,15 +2155,15 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E81" t="n">
-        <v>6533.4</v>
+        <v>4354.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B82" t="n">
         <v>2</v>
@@ -2137,15 +2174,15 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E82" t="n">
-        <v>98.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B83" t="n">
         <v>2</v>
@@ -2156,15 +2193,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>347906.1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>57013.5</v>
-      </c>
+        <v>277500</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B84" t="n">
         <v>2</v>
@@ -2175,15 +2210,15 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E84" t="n">
-        <v>962.3</v>
+        <v>1571.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B85" t="n">
         <v>2</v>
@@ -2197,12 +2232,12 @@
         <v>25000</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>8821.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B86" t="n">
         <v>3</v>
@@ -2213,15 +2248,15 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E86" t="n">
-        <v>87232.7</v>
+        <v>22383.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B87" t="n">
         <v>3</v>
@@ -2232,15 +2267,15 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E87" t="n">
-        <v>9252.200000000001</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B88" t="n">
         <v>3</v>
@@ -2251,15 +2286,15 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E88" t="n">
-        <v>882.3</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B89" t="n">
         <v>3</v>
@@ -2270,15 +2305,15 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>347906.1</v>
+        <v>277500</v>
       </c>
       <c r="E89" t="n">
-        <v>75752.10000000001</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B90" t="n">
         <v>3</v>
@@ -2289,15 +2324,15 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E90" t="n">
-        <v>1346.1</v>
+        <v>1721.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B91" t="n">
         <v>3</v>
@@ -2311,12 +2346,12 @@
         <v>25000</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>13642.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B92" t="n">
         <v>4</v>
@@ -2327,15 +2362,15 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E92" t="n">
-        <v>94912.8</v>
+        <v>26276.3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
@@ -2346,15 +2381,15 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E93" t="n">
-        <v>11543.1</v>
+        <v>8138.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B94" t="n">
         <v>4</v>
@@ -2365,15 +2400,15 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E94" t="n">
-        <v>989.2</v>
+        <v>246.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
@@ -2384,15 +2419,15 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>347906.1</v>
+        <v>277500</v>
       </c>
       <c r="E95" t="n">
-        <v>75752.10000000001</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B96" t="n">
         <v>4</v>
@@ -2403,15 +2438,15 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E96" t="n">
-        <v>1404.3</v>
+        <v>1973.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B97" t="n">
         <v>4</v>
@@ -2425,12 +2460,12 @@
         <v>25000</v>
       </c>
       <c r="E97" t="n">
-        <v>5224.1</v>
+        <v>14143.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B98" t="n">
         <v>5</v>
@@ -2441,15 +2476,15 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E98" t="n">
-        <v>122208.3</v>
+        <v>31496.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B99" t="n">
         <v>5</v>
@@ -2460,15 +2495,15 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E99" t="n">
-        <v>15971.3</v>
+        <v>12518.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B100" t="n">
         <v>5</v>
@@ -2479,15 +2514,15 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E100" t="n">
-        <v>989.2</v>
+        <v>511.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B101" t="n">
         <v>5</v>
@@ -2498,15 +2533,15 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>347906.1</v>
+        <v>215447</v>
       </c>
       <c r="E101" t="n">
-        <v>96455.60000000001</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B102" t="n">
         <v>5</v>
@@ -2517,15 +2552,15 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E102" t="n">
-        <v>1760.4</v>
+        <v>2547.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B103" t="n">
         <v>5</v>
@@ -2539,12 +2574,12 @@
         <v>25000</v>
       </c>
       <c r="E103" t="n">
-        <v>7031.8</v>
+        <v>14143.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B104" t="n">
         <v>6</v>
@@ -2555,15 +2590,15 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E104" t="n">
-        <v>212056</v>
+        <v>34696</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B105" t="n">
         <v>6</v>
@@ -2574,15 +2609,15 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E105" t="n">
-        <v>19341.9</v>
+        <v>15126.7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B106" t="n">
         <v>6</v>
@@ -2593,15 +2628,15 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E106" t="n">
-        <v>1162.1</v>
+        <v>620.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B107" t="n">
         <v>6</v>
@@ -2612,15 +2647,15 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>347906.1</v>
+        <v>215447</v>
       </c>
       <c r="E107" t="n">
-        <v>124853.9</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B108" t="n">
         <v>6</v>
@@ -2631,15 +2666,15 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E108" t="n">
-        <v>1957.3</v>
+        <v>2630.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B109" t="n">
         <v>6</v>
@@ -2653,12 +2688,12 @@
         <v>25000</v>
       </c>
       <c r="E109" t="n">
-        <v>64740.8</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B110" t="n">
         <v>7</v>
@@ -2669,15 +2704,15 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E110" t="n">
-        <v>243638.2</v>
+        <v>38484.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B111" t="n">
         <v>7</v>
@@ -2688,15 +2723,15 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E111" t="n">
-        <v>24121.6</v>
+        <v>18776.7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B112" t="n">
         <v>7</v>
@@ -2707,15 +2742,15 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E112" t="n">
-        <v>1202.2</v>
+        <v>694.4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B113" t="n">
         <v>7</v>
@@ -2726,15 +2761,15 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>347906.1</v>
+        <v>215447</v>
       </c>
       <c r="E113" t="n">
-        <v>138530.9</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B114" t="n">
         <v>7</v>
@@ -2745,15 +2780,15 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E114" t="n">
-        <v>2052.3</v>
+        <v>2695.2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B115" t="n">
         <v>7</v>
@@ -2767,12 +2802,12 @@
         <v>25000</v>
       </c>
       <c r="E115" t="n">
-        <v>77731.2</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B116" t="n">
         <v>8</v>
@@ -2783,15 +2818,15 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E116" t="n">
-        <v>282696.6</v>
+        <v>78426.7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B117" t="n">
         <v>8</v>
@@ -2802,15 +2837,15 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E117" t="n">
-        <v>26900.3</v>
+        <v>24263</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B118" t="n">
         <v>8</v>
@@ -2821,465 +2856,1833 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E118" t="n">
-        <v>1204.4</v>
+        <v>718.8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B119" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Petroleum export revenue</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>309089.4</v>
+        <v>215447</v>
       </c>
       <c r="E119" t="n">
-        <v>305051.2</v>
+        <v>36161.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mining license fees</t>
+          <t>Other revenue</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>29983.9</v>
+        <v>2650</v>
       </c>
       <c r="E120" t="n">
-        <v>32733.7</v>
+        <v>2740.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Exploration reimbursement</t>
+          <t>Tender fees</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2131.9</v>
+        <v>25000</v>
       </c>
       <c r="E121" t="n">
-        <v>1673.1</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B122" t="n">
         <v>9</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Petroleum export revenue</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E122" t="n">
-        <v>173129.4</v>
+        <v>118056.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B123" t="n">
         <v>9</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Other revenue</t>
+          <t>Mining license fees</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E123" t="n">
-        <v>2515</v>
+        <v>27069.4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B124" t="n">
         <v>9</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tender fees</t>
+          <t>Exploration reimbursement</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="E124" t="n">
-        <v>95000</v>
+        <v>1065.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Petroleum export revenue</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>309089.6</v>
+        <v>215447</v>
       </c>
       <c r="E125" t="n">
-        <v>326666.8</v>
+        <v>72448.7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mining license fees</t>
+          <t>Other revenue</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>29984</v>
+        <v>2650</v>
       </c>
       <c r="E126" t="n">
-        <v>37521.9</v>
+        <v>2929.6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Exploration reimbursement</t>
+          <t>Tender fees</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2132</v>
+        <v>25000</v>
       </c>
       <c r="E127" t="n">
-        <v>2244.5</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B128" t="n">
         <v>10</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Petroleum export revenue</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E128" t="n">
-        <v>188158.2</v>
+        <v>153134.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B129" t="n">
         <v>10</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Other revenue</t>
+          <t>Mining license fees</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E129" t="n">
-        <v>2786.5</v>
+        <v>30329.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B130" t="n">
         <v>10</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tender fees</t>
+          <t>Exploration reimbursement</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="E130" t="n">
-        <v>95955.7</v>
+        <v>1268.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Petroleum export revenue</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>309089.6</v>
+        <v>215447</v>
       </c>
       <c r="E131" t="n">
-        <v>345286.4</v>
+        <v>103737.3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Mining license fees</t>
+          <t>Other revenue</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>29984</v>
+        <v>2650</v>
       </c>
       <c r="E132" t="n">
-        <v>40617.3</v>
+        <v>3256.7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Exploration reimbursement</t>
+          <t>Tender fees</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2132</v>
+        <v>25000</v>
       </c>
       <c r="E133" t="n">
-        <v>2275.7</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B134" t="n">
         <v>11</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Petroleum export revenue</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E134" t="n">
-        <v>203450.2</v>
+        <v>182144.3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B135" t="n">
         <v>11</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Other revenue</t>
+          <t>Mining license fees</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E135" t="n">
-        <v>2987.5</v>
+        <v>32862.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B136" t="n">
         <v>11</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tender fees</t>
+          <t>Exploration reimbursement</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="E136" t="n">
-        <v>95955.7</v>
+        <v>1497.9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Petroleum export revenue</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>309089.6</v>
+        <v>215447</v>
       </c>
       <c r="E137" t="n">
-        <v>422604.5</v>
+        <v>129688.6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mining license fees</t>
+          <t>Other revenue</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>29984</v>
+        <v>2650</v>
       </c>
       <c r="E138" t="n">
-        <v>45939.6</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B139" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Exploration reimbursement</t>
+          <t>Tender fees</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2132</v>
+        <v>25000</v>
       </c>
       <c r="E139" t="n">
-        <v>3214.6</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B140" t="n">
         <v>12</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Petroleum export revenue</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E140" t="n">
-        <v>231865</v>
+        <v>216745.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B141" t="n">
         <v>12</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Other revenue</t>
+          <t>Mining license fees</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E141" t="n">
-        <v>3689.4</v>
+        <v>35598.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B142" t="n">
         <v>12</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>17500</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1966.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B143" t="n">
+        <v>12</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>215447</v>
+      </c>
+      <c r="E143" t="n">
+        <v>160996.1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B144" t="n">
+        <v>12</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2650</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3640.8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B145" t="n">
+        <v>12</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
           <t>Tender fees</t>
         </is>
       </c>
-      <c r="D142" t="n">
+      <c r="D145" t="n">
         <v>25000</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E145" t="n">
+        <v>14543</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E146" t="n">
+        <v>42230</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3201.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E148" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>38118.7</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>811.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E152" t="n">
+        <v>64607.3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E153" t="n">
+        <v>6533.4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E154" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>57013.5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>962.3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E158" t="n">
+        <v>87232.7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E159" t="n">
+        <v>9252.200000000001</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E160" t="n">
+        <v>882.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>75752.10000000001</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1346.1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B164" t="n">
+        <v>4</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E164" t="n">
+        <v>94912.8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11543.1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E166" t="n">
+        <v>989.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B167" t="n">
+        <v>4</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>75752.10000000001</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1404.3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B169" t="n">
+        <v>4</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5224.1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E170" t="n">
+        <v>122208.3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E171" t="n">
+        <v>15971.3</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E172" t="n">
+        <v>989.2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>96455.60000000001</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1760.4</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E175" t="n">
+        <v>7031.8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B176" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E176" t="n">
+        <v>212056</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B177" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E177" t="n">
+        <v>19341.9</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B178" t="n">
+        <v>6</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1162.1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B179" t="n">
+        <v>6</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>124853.9</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B180" t="n">
+        <v>6</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1957.3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B181" t="n">
+        <v>6</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E181" t="n">
+        <v>64740.8</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B182" t="n">
+        <v>7</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E182" t="n">
+        <v>243638.2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B183" t="n">
+        <v>7</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E183" t="n">
+        <v>24121.6</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B184" t="n">
+        <v>7</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1202.2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B185" t="n">
+        <v>7</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>138530.9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B186" t="n">
+        <v>7</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2052.3</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B187" t="n">
+        <v>7</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E187" t="n">
+        <v>77731.2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B188" t="n">
+        <v>8</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E188" t="n">
+        <v>282696.6</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B189" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E189" t="n">
+        <v>26900.3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1204.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B191" t="n">
+        <v>9</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>309089.4</v>
+      </c>
+      <c r="E191" t="n">
+        <v>305051.2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B192" t="n">
+        <v>9</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E192" t="n">
+        <v>32733.7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B193" t="n">
+        <v>9</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1673.1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B194" t="n">
+        <v>9</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E194" t="n">
+        <v>173129.4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B195" t="n">
+        <v>9</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B196" t="n">
+        <v>9</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E196" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B197" t="n">
+        <v>10</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>309089.6</v>
+      </c>
+      <c r="E197" t="n">
+        <v>326666.8</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B198" t="n">
+        <v>10</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>29984</v>
+      </c>
+      <c r="E198" t="n">
+        <v>37521.9</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B199" t="n">
+        <v>10</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2244.5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B200" t="n">
+        <v>10</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E200" t="n">
+        <v>188158.2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B201" t="n">
+        <v>10</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2786.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B202" t="n">
+        <v>10</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E202" t="n">
+        <v>95955.7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B203" t="n">
+        <v>11</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>309089.6</v>
+      </c>
+      <c r="E203" t="n">
+        <v>345286.4</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B204" t="n">
+        <v>11</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>29984</v>
+      </c>
+      <c r="E204" t="n">
+        <v>40617.3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B205" t="n">
+        <v>11</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2275.7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B206" t="n">
+        <v>11</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E206" t="n">
+        <v>203450.2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B207" t="n">
+        <v>11</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2987.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B208" t="n">
+        <v>11</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E208" t="n">
+        <v>95955.7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B209" t="n">
+        <v>12</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>309089.6</v>
+      </c>
+      <c r="E209" t="n">
+        <v>422604.5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B210" t="n">
+        <v>12</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Mining license fees</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>29984</v>
+      </c>
+      <c r="E210" t="n">
+        <v>45939.6</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B211" t="n">
+        <v>12</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Exploration reimbursement</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3214.6</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B212" t="n">
+        <v>12</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Petroleum export revenue</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E212" t="n">
+        <v>231865</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B213" t="n">
+        <v>12</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3689.4</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B214" t="n">
+        <v>12</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Tender fees</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E214" t="n">
         <v>137895.9</v>
       </c>
     </row>
@@ -3294,7 +4697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3326,7 +4729,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -3337,15 +4740,15 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E2" t="n">
-        <v>5564.8</v>
+        <v>16685.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -3356,15 +4759,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>2432.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -3375,15 +4778,15 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E4" t="n">
-        <v>72.59999999999999</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -3394,13 +4797,15 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>277500</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>183200</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14014.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -3411,15 +4816,15 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E6" t="n">
-        <v>200.8</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -3430,15 +4835,15 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E7" t="n">
-        <v>2479.5</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -3449,15 +4854,15 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E8" t="n">
-        <v>14840.7</v>
+        <v>36582.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -3468,15 +4873,15 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E9" t="n">
-        <v>4354.5</v>
+        <v>3637.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="n">
         <v>2</v>
@@ -3487,15 +4892,15 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E10" t="n">
-        <v>93.40000000000001</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B11" t="n">
         <v>2</v>
@@ -3506,13 +4911,15 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>277500</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>183200</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30860</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B12" t="n">
         <v>2</v>
@@ -3523,15 +4930,15 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E12" t="n">
-        <v>1571.3</v>
+        <v>1034.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
@@ -3542,15 +4949,15 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E13" t="n">
-        <v>8821.5</v>
+        <v>863.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
@@ -3561,15 +4968,15 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E14" t="n">
-        <v>22383.8</v>
+        <v>57177.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B15" t="n">
         <v>3</v>
@@ -3580,15 +4987,15 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E15" t="n">
-        <v>5962</v>
+        <v>5622.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
@@ -3599,15 +5006,15 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E16" t="n">
-        <v>197</v>
+        <v>247.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B17" t="n">
         <v>3</v>
@@ -3618,15 +5025,15 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>277500</v>
+        <v>183200</v>
       </c>
       <c r="E17" t="n">
-        <v>861.3</v>
+        <v>46592.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B18" t="n">
         <v>3</v>
@@ -3637,15 +5044,15 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E18" t="n">
-        <v>1721.4</v>
+        <v>1197.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B19" t="n">
         <v>3</v>
@@ -3656,15 +5063,15 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E19" t="n">
-        <v>13642.2</v>
+        <v>3518.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
@@ -3675,15 +5082,15 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>354050</v>
+        <v>235400</v>
       </c>
       <c r="E20" t="n">
-        <v>26276.3</v>
+        <v>84426.39999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
@@ -3694,15 +5101,15 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E21" t="n">
-        <v>8138.3</v>
+        <v>7243.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
@@ -3713,15 +5120,15 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E22" t="n">
-        <v>246.6</v>
+        <v>284.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
@@ -3732,15 +5139,15 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>277500</v>
+        <v>183200</v>
       </c>
       <c r="E23" t="n">
-        <v>1774.9</v>
+        <v>65710.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
@@ -3751,15 +5158,15 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E24" t="n">
-        <v>1973.4</v>
+        <v>1377.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
@@ -3770,15 +5177,15 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E25" t="n">
-        <v>14143.2</v>
+        <v>9811.200000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B26" t="n">
         <v>5</v>
@@ -3789,15 +5196,15 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E26" t="n">
-        <v>31496.3</v>
+        <v>108155.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
@@ -3808,15 +5215,15 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E27" t="n">
-        <v>12518.9</v>
+        <v>10498.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
@@ -3827,15 +5234,15 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E28" t="n">
-        <v>511.5</v>
+        <v>306.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
@@ -3846,15 +5253,15 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E29" t="n">
-        <v>1774.9</v>
+        <v>85920</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
@@ -3865,15 +5272,15 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E30" t="n">
-        <v>2547.9</v>
+        <v>1619.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
@@ -3884,15 +5291,15 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E31" t="n">
-        <v>14143.2</v>
+        <v>9811.200000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B32" t="n">
         <v>6</v>
@@ -3903,15 +5310,15 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E32" t="n">
-        <v>34696</v>
+        <v>137933.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B33" t="n">
         <v>6</v>
@@ -3922,15 +5329,15 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E33" t="n">
-        <v>15126.7</v>
+        <v>14591.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B34" t="n">
         <v>6</v>
@@ -3941,15 +5348,15 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E34" t="n">
-        <v>620.6</v>
+        <v>415.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B35" t="n">
         <v>6</v>
@@ -3960,15 +5367,15 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E35" t="n">
-        <v>1774.9</v>
+        <v>104956.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B36" t="n">
         <v>6</v>
@@ -3979,15 +5386,15 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E36" t="n">
-        <v>2630.9</v>
+        <v>1771.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B37" t="n">
         <v>6</v>
@@ -3998,15 +5405,15 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E37" t="n">
-        <v>14543</v>
+        <v>16198.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B38" t="n">
         <v>7</v>
@@ -4017,15 +5424,15 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E38" t="n">
-        <v>38484.2</v>
+        <v>164859.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B39" t="n">
         <v>7</v>
@@ -4036,15 +5443,15 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E39" t="n">
-        <v>18776.7</v>
+        <v>16609.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B40" t="n">
         <v>7</v>
@@ -4055,15 +5462,15 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E40" t="n">
-        <v>694.4</v>
+        <v>572.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B41" t="n">
         <v>7</v>
@@ -4074,15 +5481,15 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E41" t="n">
-        <v>1774.9</v>
+        <v>124837.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B42" t="n">
         <v>7</v>
@@ -4093,15 +5500,15 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E42" t="n">
-        <v>2695.2</v>
+        <v>2171.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B43" t="n">
         <v>7</v>
@@ -4112,15 +5519,15 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E43" t="n">
-        <v>14543</v>
+        <v>20668.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B44" t="n">
         <v>8</v>
@@ -4131,15 +5538,15 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>291997</v>
+        <v>235400</v>
       </c>
       <c r="E44" t="n">
-        <v>78426.7</v>
+        <v>191255.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B45" t="n">
         <v>8</v>
@@ -4150,15 +5557,15 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E45" t="n">
-        <v>24263</v>
+        <v>21870.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B46" t="n">
         <v>8</v>
@@ -4169,15 +5576,15 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E46" t="n">
-        <v>718.8</v>
+        <v>824.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B47" t="n">
         <v>8</v>
@@ -4188,15 +5595,15 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>215447</v>
+        <v>183200</v>
       </c>
       <c r="E47" t="n">
-        <v>36161.3</v>
+        <v>143767.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B48" t="n">
         <v>8</v>
@@ -4207,15 +5614,15 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E48" t="n">
-        <v>2740.5</v>
+        <v>2535.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B49" t="n">
         <v>8</v>
@@ -4226,15 +5633,15 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E49" t="n">
-        <v>14543</v>
+        <v>22256.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B50" t="n">
         <v>9</v>
@@ -4245,15 +5652,15 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E50" t="n">
-        <v>118056.5</v>
+        <v>221006.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B51" t="n">
         <v>9</v>
@@ -4264,15 +5671,15 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E51" t="n">
-        <v>27069.4</v>
+        <v>24526.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B52" t="n">
         <v>9</v>
@@ -4283,15 +5690,15 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E52" t="n">
-        <v>1065.7</v>
+        <v>3153.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B53" t="n">
         <v>9</v>
@@ -4302,15 +5709,15 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E53" t="n">
-        <v>72448.7</v>
+        <v>161552.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B54" t="n">
         <v>9</v>
@@ -4321,15 +5728,15 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E54" t="n">
-        <v>2929.6</v>
+        <v>2759</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B55" t="n">
         <v>9</v>
@@ -4340,15 +5747,15 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E55" t="n">
-        <v>14543</v>
+        <v>29014.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B56" t="n">
         <v>10</v>
@@ -4359,15 +5766,15 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E56" t="n">
-        <v>153134.8</v>
+        <v>228926.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B57" t="n">
         <v>10</v>
@@ -4378,15 +5785,15 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E57" t="n">
-        <v>30329.5</v>
+        <v>27925.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B58" t="n">
         <v>10</v>
@@ -4397,15 +5804,15 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E58" t="n">
-        <v>1268.2</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B59" t="n">
         <v>10</v>
@@ -4416,15 +5823,15 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E59" t="n">
-        <v>103737.3</v>
+        <v>164612.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B60" t="n">
         <v>10</v>
@@ -4435,15 +5842,15 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E60" t="n">
-        <v>3256.7</v>
+        <v>3567.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B61" t="n">
         <v>10</v>
@@ -4454,15 +5861,15 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E61" t="n">
-        <v>14543</v>
+        <v>29466.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B62" t="n">
         <v>11</v>
@@ -4473,15 +5880,15 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E62" t="n">
-        <v>182144.3</v>
+        <v>248066.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B63" t="n">
         <v>11</v>
@@ -4492,15 +5899,15 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E63" t="n">
-        <v>32862.9</v>
+        <v>30795.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B64" t="n">
         <v>11</v>
@@ -4511,15 +5918,15 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E64" t="n">
-        <v>1497.9</v>
+        <v>3534.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B65" t="n">
         <v>11</v>
@@ -4530,15 +5937,15 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E65" t="n">
-        <v>129688.6</v>
+        <v>180419.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B66" t="n">
         <v>11</v>
@@ -4549,15 +5956,15 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E66" t="n">
-        <v>3552</v>
+        <v>3693.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B67" t="n">
         <v>11</v>
@@ -4568,15 +5975,15 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E67" t="n">
-        <v>14543</v>
+        <v>29623.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B68" t="n">
         <v>12</v>
@@ -4587,15 +5994,15 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>291997</v>
+        <v>265400</v>
       </c>
       <c r="E68" t="n">
-        <v>216745.2</v>
+        <v>268696.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B69" t="n">
         <v>12</v>
@@ -4606,15 +6013,15 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>31400</v>
+        <v>31200</v>
       </c>
       <c r="E69" t="n">
-        <v>35598.5</v>
+        <v>32770.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B70" t="n">
         <v>12</v>
@@ -4625,15 +6032,15 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>17500</v>
+        <v>2500</v>
       </c>
       <c r="E70" t="n">
-        <v>1966.8</v>
+        <v>4409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B71" t="n">
         <v>12</v>
@@ -4644,15 +6051,15 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>215447</v>
+        <v>213200</v>
       </c>
       <c r="E71" t="n">
-        <v>160996.1</v>
+        <v>198145.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B72" t="n">
         <v>12</v>
@@ -4663,15 +6070,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2650</v>
+        <v>2500</v>
       </c>
       <c r="E72" t="n">
-        <v>3640.8</v>
+        <v>3748.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B73" t="n">
         <v>12</v>
@@ -4682,15 +6089,15 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="E73" t="n">
-        <v>14543</v>
+        <v>29623.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B74" t="n">
         <v>1</v>
@@ -4701,15 +6108,15 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E74" t="n">
-        <v>42230</v>
+        <v>5564.8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B75" t="n">
         <v>1</v>
@@ -4720,15 +6127,15 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E75" t="n">
-        <v>3201.7</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B76" t="n">
         <v>1</v>
@@ -4739,15 +6146,15 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E76" t="n">
-        <v>98.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B77" t="n">
         <v>1</v>
@@ -4758,15 +6165,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>347906.1</v>
-      </c>
-      <c r="E77" t="n">
-        <v>38118.7</v>
-      </c>
+        <v>277500</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B78" t="n">
         <v>1</v>
@@ -4777,15 +6182,15 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E78" t="n">
-        <v>811.5</v>
+        <v>200.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B79" t="n">
         <v>1</v>
@@ -4799,12 +6204,12 @@
         <v>25000</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>2479.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B80" t="n">
         <v>2</v>
@@ -4815,15 +6220,15 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E80" t="n">
-        <v>64607.3</v>
+        <v>14840.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B81" t="n">
         <v>2</v>
@@ -4834,15 +6239,15 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E81" t="n">
-        <v>6533.4</v>
+        <v>4354.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B82" t="n">
         <v>2</v>
@@ -4853,15 +6258,15 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E82" t="n">
-        <v>98.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B83" t="n">
         <v>2</v>
@@ -4872,15 +6277,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>347906.1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>57013.5</v>
-      </c>
+        <v>277500</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B84" t="n">
         <v>2</v>
@@ -4891,15 +6294,15 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E84" t="n">
-        <v>962.3</v>
+        <v>1571.3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B85" t="n">
         <v>2</v>
@@ -4913,12 +6316,12 @@
         <v>25000</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>8821.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B86" t="n">
         <v>3</v>
@@ -4929,15 +6332,15 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E86" t="n">
-        <v>87232.7</v>
+        <v>22383.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B87" t="n">
         <v>3</v>
@@ -4948,15 +6351,15 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E87" t="n">
-        <v>9252.200000000001</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B88" t="n">
         <v>3</v>
@@ -4967,15 +6370,15 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E88" t="n">
-        <v>882.3</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B89" t="n">
         <v>3</v>
@@ -4986,15 +6389,15 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>347906.1</v>
+        <v>277500</v>
       </c>
       <c r="E89" t="n">
-        <v>75752.10000000001</v>
+        <v>861.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B90" t="n">
         <v>3</v>
@@ -5005,15 +6408,15 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E90" t="n">
-        <v>1346.1</v>
+        <v>1721.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B91" t="n">
         <v>3</v>
@@ -5027,12 +6430,12 @@
         <v>25000</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>13642.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B92" t="n">
         <v>4</v>
@@ -5043,15 +6446,15 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>407301</v>
+        <v>354050</v>
       </c>
       <c r="E92" t="n">
-        <v>94912.8</v>
+        <v>26276.3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B93" t="n">
         <v>4</v>
@@ -5062,15 +6465,15 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E93" t="n">
-        <v>11543.1</v>
+        <v>8138.3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B94" t="n">
         <v>4</v>
@@ -5081,15 +6484,15 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E94" t="n">
-        <v>989.2</v>
+        <v>246.6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B95" t="n">
         <v>4</v>
@@ -5100,15 +6503,15 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>347906.1</v>
+        <v>277500</v>
       </c>
       <c r="E95" t="n">
-        <v>75752.10000000001</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B96" t="n">
         <v>4</v>
@@ -5119,15 +6522,15 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E96" t="n">
-        <v>1404.3</v>
+        <v>1973.4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B97" t="n">
         <v>4</v>
@@ -5141,12 +6544,12 @@
         <v>25000</v>
       </c>
       <c r="E97" t="n">
-        <v>5224.1</v>
+        <v>14143.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B98" t="n">
         <v>5</v>
@@ -5157,15 +6560,15 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E98" t="n">
-        <v>122208.3</v>
+        <v>31496.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B99" t="n">
         <v>5</v>
@@ -5176,15 +6579,15 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E99" t="n">
-        <v>15971.3</v>
+        <v>12518.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B100" t="n">
         <v>5</v>
@@ -5195,15 +6598,15 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E100" t="n">
-        <v>989.2</v>
+        <v>511.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B101" t="n">
         <v>5</v>
@@ -5214,15 +6617,15 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>347906.1</v>
+        <v>215447</v>
       </c>
       <c r="E101" t="n">
-        <v>96455.60000000001</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B102" t="n">
         <v>5</v>
@@ -5233,15 +6636,15 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E102" t="n">
-        <v>1760.4</v>
+        <v>2547.9</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B103" t="n">
         <v>5</v>
@@ -5255,12 +6658,12 @@
         <v>25000</v>
       </c>
       <c r="E103" t="n">
-        <v>7031.8</v>
+        <v>14143.2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B104" t="n">
         <v>6</v>
@@ -5271,15 +6674,15 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E104" t="n">
-        <v>212056</v>
+        <v>34696</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B105" t="n">
         <v>6</v>
@@ -5290,15 +6693,15 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E105" t="n">
-        <v>19341.9</v>
+        <v>15126.7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B106" t="n">
         <v>6</v>
@@ -5309,15 +6712,15 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E106" t="n">
-        <v>1162.1</v>
+        <v>620.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B107" t="n">
         <v>6</v>
@@ -5328,15 +6731,15 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>347906.1</v>
+        <v>215447</v>
       </c>
       <c r="E107" t="n">
-        <v>124853.9</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B108" t="n">
         <v>6</v>
@@ -5347,15 +6750,15 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E108" t="n">
-        <v>1957.3</v>
+        <v>2630.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B109" t="n">
         <v>6</v>
@@ -5369,12 +6772,12 @@
         <v>25000</v>
       </c>
       <c r="E109" t="n">
-        <v>64740.8</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B110" t="n">
         <v>7</v>
@@ -5385,15 +6788,15 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E110" t="n">
-        <v>243638.2</v>
+        <v>38484.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B111" t="n">
         <v>7</v>
@@ -5404,15 +6807,15 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E111" t="n">
-        <v>24121.6</v>
+        <v>18776.7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B112" t="n">
         <v>7</v>
@@ -5423,15 +6826,15 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E112" t="n">
-        <v>1202.2</v>
+        <v>694.4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B113" t="n">
         <v>7</v>
@@ -5442,15 +6845,15 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>347906.1</v>
+        <v>215447</v>
       </c>
       <c r="E113" t="n">
-        <v>138530.9</v>
+        <v>1774.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B114" t="n">
         <v>7</v>
@@ -5461,15 +6864,15 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2279.1</v>
+        <v>2650</v>
       </c>
       <c r="E114" t="n">
-        <v>2052.3</v>
+        <v>2695.2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B115" t="n">
         <v>7</v>
@@ -5483,12 +6886,12 @@
         <v>25000</v>
       </c>
       <c r="E115" t="n">
-        <v>77731.2</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B116" t="n">
         <v>8</v>
@@ -5499,15 +6902,15 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>407301</v>
+        <v>291997</v>
       </c>
       <c r="E116" t="n">
-        <v>282696.6</v>
+        <v>78426.7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B117" t="n">
         <v>8</v>
@@ -5518,15 +6921,15 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>29983.9</v>
+        <v>31400</v>
       </c>
       <c r="E117" t="n">
-        <v>26900.3</v>
+        <v>24263</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B118" t="n">
         <v>8</v>
@@ -5537,465 +6940,1833 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2131.9</v>
+        <v>17500</v>
       </c>
       <c r="E118" t="n">
-        <v>1204.4</v>
+        <v>718.8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B119" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>БҮГД</t>
+          <t>Газрын тосны экспорт</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>309089.4</v>
+        <v>215447</v>
       </c>
       <c r="E119" t="n">
-        <v>305051.2</v>
+        <v>36161.3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+          <t>Бусад орлого</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>29983.9</v>
+        <v>2650</v>
       </c>
       <c r="E120" t="n">
-        <v>32733.7</v>
+        <v>2740.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Хайгуулын ордын нөхөн төлбөр</t>
+          <t>Сонгон шалгаруулалт</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>2131.9</v>
+        <v>25000</v>
       </c>
       <c r="E121" t="n">
-        <v>1673.1</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B122" t="n">
         <v>9</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Газрын тосны экспорт</t>
+          <t>БҮГД</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E122" t="n">
-        <v>173129.4</v>
+        <v>118056.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B123" t="n">
         <v>9</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Бусад орлого</t>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E123" t="n">
-        <v>2515</v>
+        <v>27069.4</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B124" t="n">
         <v>9</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Сонгон шалгаруулалт</t>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="E124" t="n">
-        <v>95000</v>
+        <v>1065.7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>БҮГД</t>
+          <t>Газрын тосны экспорт</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>309089.6</v>
+        <v>215447</v>
       </c>
       <c r="E125" t="n">
-        <v>326666.8</v>
+        <v>72448.7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B126" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+          <t>Бусад орлого</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>29984</v>
+        <v>2650</v>
       </c>
       <c r="E126" t="n">
-        <v>37521.9</v>
+        <v>2929.6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B127" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Хайгуулын ордын нөхөн төлбөр</t>
+          <t>Сонгон шалгаруулалт</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2132</v>
+        <v>25000</v>
       </c>
       <c r="E127" t="n">
-        <v>2244.5</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B128" t="n">
         <v>10</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Газрын тосны экспорт</t>
+          <t>БҮГД</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E128" t="n">
-        <v>188158.2</v>
+        <v>153134.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B129" t="n">
         <v>10</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Бусад орлого</t>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E129" t="n">
-        <v>2786.5</v>
+        <v>30329.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B130" t="n">
         <v>10</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Сонгон шалгаруулалт</t>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="E130" t="n">
-        <v>95955.7</v>
+        <v>1268.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>БҮГД</t>
+          <t>Газрын тосны экспорт</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>309089.6</v>
+        <v>215447</v>
       </c>
       <c r="E131" t="n">
-        <v>345286.4</v>
+        <v>103737.3</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+          <t>Бусад орлого</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>29984</v>
+        <v>2650</v>
       </c>
       <c r="E132" t="n">
-        <v>40617.3</v>
+        <v>3256.7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Хайгуулын ордын нөхөн төлбөр</t>
+          <t>Сонгон шалгаруулалт</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>2132</v>
+        <v>25000</v>
       </c>
       <c r="E133" t="n">
-        <v>2275.7</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B134" t="n">
         <v>11</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Газрын тосны экспорт</t>
+          <t>БҮГД</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E134" t="n">
-        <v>203450.2</v>
+        <v>182144.3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B135" t="n">
         <v>11</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Бусад орлого</t>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E135" t="n">
-        <v>2987.5</v>
+        <v>32862.9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B136" t="n">
         <v>11</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Сонгон шалгаруулалт</t>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>25000</v>
+        <v>17500</v>
       </c>
       <c r="E136" t="n">
-        <v>95955.7</v>
+        <v>1497.9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B137" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>БҮГД</t>
+          <t>Газрын тосны экспорт</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>309089.6</v>
+        <v>215447</v>
       </c>
       <c r="E137" t="n">
-        <v>422604.5</v>
+        <v>129688.6</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B138" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+          <t>Бусад орлого</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>29984</v>
+        <v>2650</v>
       </c>
       <c r="E138" t="n">
-        <v>45939.6</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B139" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Хайгуулын ордын нөхөн төлбөр</t>
+          <t>Сонгон шалгаруулалт</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2132</v>
+        <v>25000</v>
       </c>
       <c r="E139" t="n">
-        <v>3214.6</v>
+        <v>14543</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B140" t="n">
         <v>12</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Газрын тосны экспорт</t>
+          <t>БҮГД</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>249694.5</v>
+        <v>291997</v>
       </c>
       <c r="E140" t="n">
-        <v>231865</v>
+        <v>216745.2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B141" t="n">
         <v>12</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Бусад орлого</t>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2279.1</v>
+        <v>31400</v>
       </c>
       <c r="E141" t="n">
-        <v>3689.4</v>
+        <v>35598.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B142" t="n">
         <v>12</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>17500</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1966.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B143" t="n">
+        <v>12</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>215447</v>
+      </c>
+      <c r="E143" t="n">
+        <v>160996.1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B144" t="n">
+        <v>12</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2650</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3640.8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B145" t="n">
+        <v>12</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
           <t>Сонгон шалгаруулалт</t>
         </is>
       </c>
-      <c r="D142" t="n">
+      <c r="D145" t="n">
         <v>25000</v>
       </c>
-      <c r="E142" t="n">
+      <c r="E145" t="n">
+        <v>14543</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E146" t="n">
+        <v>42230</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3201.7</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E148" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>38118.7</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>811.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B152" t="n">
+        <v>2</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E152" t="n">
+        <v>64607.3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B153" t="n">
+        <v>2</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E153" t="n">
+        <v>6533.4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B154" t="n">
+        <v>2</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E154" t="n">
+        <v>98.09999999999999</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B155" t="n">
+        <v>2</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>57013.5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>962.3</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B158" t="n">
+        <v>3</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E158" t="n">
+        <v>87232.7</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B159" t="n">
+        <v>3</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E159" t="n">
+        <v>9252.200000000001</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" t="n">
+        <v>3</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E160" t="n">
+        <v>882.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>75752.10000000001</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B162" t="n">
+        <v>3</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1346.1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B163" t="n">
+        <v>3</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B164" t="n">
+        <v>4</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E164" t="n">
+        <v>94912.8</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E165" t="n">
+        <v>11543.1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E166" t="n">
+        <v>989.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B167" t="n">
+        <v>4</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>75752.10000000001</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B168" t="n">
+        <v>4</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1404.3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B169" t="n">
+        <v>4</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E169" t="n">
+        <v>5224.1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E170" t="n">
+        <v>122208.3</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E171" t="n">
+        <v>15971.3</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E172" t="n">
+        <v>989.2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>96455.60000000001</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1760.4</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E175" t="n">
+        <v>7031.8</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B176" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E176" t="n">
+        <v>212056</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B177" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E177" t="n">
+        <v>19341.9</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B178" t="n">
+        <v>6</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1162.1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B179" t="n">
+        <v>6</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>124853.9</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B180" t="n">
+        <v>6</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1957.3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B181" t="n">
+        <v>6</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E181" t="n">
+        <v>64740.8</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B182" t="n">
+        <v>7</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E182" t="n">
+        <v>243638.2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B183" t="n">
+        <v>7</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E183" t="n">
+        <v>24121.6</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B184" t="n">
+        <v>7</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1202.2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B185" t="n">
+        <v>7</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>347906.1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>138530.9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B186" t="n">
+        <v>7</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2052.3</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B187" t="n">
+        <v>7</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E187" t="n">
+        <v>77731.2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B188" t="n">
+        <v>8</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>407301</v>
+      </c>
+      <c r="E188" t="n">
+        <v>282696.6</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B189" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E189" t="n">
+        <v>26900.3</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1204.4</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B191" t="n">
+        <v>9</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>309089.4</v>
+      </c>
+      <c r="E191" t="n">
+        <v>305051.2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B192" t="n">
+        <v>9</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>29983.9</v>
+      </c>
+      <c r="E192" t="n">
+        <v>32733.7</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B193" t="n">
+        <v>9</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>2131.9</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1673.1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B194" t="n">
+        <v>9</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E194" t="n">
+        <v>173129.4</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B195" t="n">
+        <v>9</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B196" t="n">
+        <v>9</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E196" t="n">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B197" t="n">
+        <v>10</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>309089.6</v>
+      </c>
+      <c r="E197" t="n">
+        <v>326666.8</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B198" t="n">
+        <v>10</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>29984</v>
+      </c>
+      <c r="E198" t="n">
+        <v>37521.9</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B199" t="n">
+        <v>10</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2244.5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B200" t="n">
+        <v>10</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E200" t="n">
+        <v>188158.2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B201" t="n">
+        <v>10</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2786.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B202" t="n">
+        <v>10</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E202" t="n">
+        <v>95955.7</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B203" t="n">
+        <v>11</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>309089.6</v>
+      </c>
+      <c r="E203" t="n">
+        <v>345286.4</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B204" t="n">
+        <v>11</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>29984</v>
+      </c>
+      <c r="E204" t="n">
+        <v>40617.3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B205" t="n">
+        <v>11</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2275.7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B206" t="n">
+        <v>11</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E206" t="n">
+        <v>203450.2</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B207" t="n">
+        <v>11</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>2987.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B208" t="n">
+        <v>11</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E208" t="n">
+        <v>95955.7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B209" t="n">
+        <v>12</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>309089.6</v>
+      </c>
+      <c r="E209" t="n">
+        <v>422604.5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B210" t="n">
+        <v>12</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>29984</v>
+      </c>
+      <c r="E210" t="n">
+        <v>45939.6</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B211" t="n">
+        <v>12</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>2132</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3214.6</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B212" t="n">
+        <v>12</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>249694.5</v>
+      </c>
+      <c r="E212" t="n">
+        <v>231865</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B213" t="n">
+        <v>12</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>2279.1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3689.4</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B214" t="n">
+        <v>12</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E214" t="n">
         <v>137895.9</v>
       </c>
     </row>

--- a/data.mn/public/datasets/mrpam-budget-revenue.xlsx
+++ b/data.mn/public/datasets/mrpam-budget-revenue.xlsx
@@ -28,6 +28,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="002E4057"/>
       </patternFill>
     </fill>
   </fills>
@@ -425,13 +426,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,12 +439,15 @@
         </is>
       </c>
       <c r="B1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -456,11 +457,9 @@
           <t>(Cont.Table 1.5) Mining license Area size Number Share to total Hectare Share to total Construction Rock</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>19024.8</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -468,11 +467,9 @@
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2793.1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -480,11 +477,9 @@
           <t>Bazalit</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>1370.9</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -492,11 +487,9 @@
           <t>Bitumen</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>601.5</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -504,11 +497,9 @@
           <t>Common Construction</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>599.1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -516,11 +507,9 @@
           <t>Common mineral</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>183.5</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -528,11 +517,9 @@
           <t>Concentrated metal</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>4533.3</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -540,11 +527,9 @@
           <t>Construction materials</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>2009.2</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -552,11 +537,9 @@
           <t>Copper</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>21148.8</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -564,11 +547,9 @@
           <t>Face stone</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>2618.6</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -576,11 +557,9 @@
           <t>Glauberic salt</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>1449</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -588,11 +567,9 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>16385.5</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,11 +577,9 @@
           <t>Gold (placer)</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>33619.7</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -612,11 +587,9 @@
           <t>Gold ore</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>6206</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -624,11 +597,9 @@
           <t>Gold оre</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>4668.6</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -636,11 +607,9 @@
           <t>Granite</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>275.3</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -648,11 +617,9 @@
           <t>Graphite</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>3000.6</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -660,11 +627,9 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>5593.9</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -672,11 +637,9 @@
           <t>Keramzite Clay</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>207.8</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -684,11 +647,9 @@
           <t>Lithium</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>4720.2</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -696,9 +657,7 @@
           <t>Mining license fee</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>273678</v>
       </c>
     </row>
@@ -708,9 +667,7 @@
           <t>Other revenue</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>24677.8</v>
       </c>
     </row>
@@ -720,11 +677,9 @@
           <t>Perlit</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>771.5</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -732,9 +687,7 @@
           <t>Petroleum export revenue</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>1560266.3</v>
       </c>
     </row>
@@ -744,11 +697,9 @@
           <t>Precious stones</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>593.2</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -756,11 +707,9 @@
           <t>Quartz</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>525.4</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -768,9 +717,7 @@
           <t>Reimbursement for state-funded exploration</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>16033.5</v>
       </c>
     </row>
@@ -780,11 +727,9 @@
           <t>Sand</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>21927.3</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -792,11 +737,9 @@
           <t>Silicium</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="C30" t="n">
         <v>9587.700000000001</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -804,11 +747,9 @@
           <t>Silver</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="C31" t="n">
         <v>1050.4</v>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -816,9 +757,7 @@
           <t>Tender revenue</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>674535.2</v>
       </c>
     </row>
@@ -828,9 +767,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>2549190.8</v>
       </c>
     </row>
@@ -840,11 +777,9 @@
           <t>Tungsten</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="C34" t="n">
         <v>2833.9</v>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -852,11 +787,9 @@
           <t>Zinc</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="C35" t="n">
         <v>1969.8</v>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -864,13 +797,12 @@
           <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="C36" t="n">
         <v>199646.1</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>245388.4</v>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -878,13 +810,12 @@
           <t>Бусад орлого</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="C37" t="n">
         <v>35777.2</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>23028</v>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -892,13 +823,12 @@
           <t>БҮГД</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="C38" t="n">
         <v>2126263.2</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>2121407.8</v>
       </c>
-      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -906,13 +836,12 @@
           <t>Газрын тосны экспорт</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="C39" t="n">
         <v>1601164.4</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>1498017.5</v>
       </c>
-      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -920,13 +849,12 @@
           <t>Сонгон шалгаруулалт</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="C40" t="n">
         <v>279981.9</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>338645.5</v>
       </c>
-      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -934,13 +862,12 @@
           <t>Улсын төсвийн хөрөнгөөр хайгуул хийсэн ордын нөхөн төлбөр</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="C41" t="n">
         <v>9693.799999999999</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>16328.4</v>
       </c>
-      <c r="D41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -953,13 +880,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -969,12 +893,15 @@
         </is>
       </c>
       <c r="B1" s="1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -984,11 +911,9 @@
           <t>(Cont.Table 1.5) Mining license Area size Number Share to total Hectare Share to total Construction Rock</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>19024.8</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -996,11 +921,9 @@
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>2793.1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1008,11 +931,9 @@
           <t>Bazalit</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>1370.9</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1020,11 +941,9 @@
           <t>Bitumen</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>601.5</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1032,11 +951,9 @@
           <t>Common Construction</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>599.1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1044,11 +961,9 @@
           <t>Common mineral</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>183.5</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1056,11 +971,9 @@
           <t>Concentrated metal</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>4533.3</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1068,11 +981,9 @@
           <t>Construction materials</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>2009.2</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1080,11 +991,9 @@
           <t>Copper</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>21148.8</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1092,11 +1001,9 @@
           <t>Face stone</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>2618.6</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1104,11 +1011,9 @@
           <t>Glauberic salt</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>1449</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1116,11 +1021,9 @@
           <t>Gold</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>16385.5</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1128,11 +1031,9 @@
           <t>Gold (placer)</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>33619.7</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1140,11 +1041,9 @@
           <t>Gold ore</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>6206</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1152,11 +1051,9 @@
           <t>Gold оre</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>4668.6</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1164,11 +1061,9 @@
           <t>Granite</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>275.3</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1176,11 +1071,9 @@
           <t>Graphite</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>3000.6</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1188,11 +1081,9 @@
           <t>Iron</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>5593.9</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1200,11 +1091,9 @@
           <t>Keramzite Clay</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>207.8</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1212,11 +1101,9 @@
           <t>Lithium</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>4720.2</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1224,11 +1111,9 @@
           <t>Perlit</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="C22" t="n">
         <v>771.5</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1236,11 +1121,9 @@
           <t>Precious stones</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="C23" t="n">
         <v>593.2</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1248,11 +1131,9 @@
           <t>Quartz</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>525.4</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1260,11 +1141,9 @@
           <t>Sand</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="C25" t="n">
         <v>21927.3</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1272,11 +1151,9 @@
           <t>Silicium</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>9587.700000000001</v>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1284,11 +1161,9 @@
           <t>Silver</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>1050.4</v>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1296,11 +1171,9 @@
           <t>Tungsten</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="C28" t="n">
         <v>2833.9</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1308,11 +1181,9 @@
           <t>Zinc</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>1969.8</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1321,12 +1192,15 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>217812.4</v>
+      </c>
+      <c r="C30" t="n">
         <v>199646.1</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>245388.4</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>273678</v>
       </c>
     </row>
@@ -1337,12 +1211,15 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>29460.5</v>
+      </c>
+      <c r="C31" t="n">
         <v>35777.2</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>23028</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>24677.8</v>
       </c>
     </row>
@@ -1353,12 +1230,15 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>922249.6</v>
+      </c>
+      <c r="C32" t="n">
         <v>2126263.2</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>2121407.8</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>2549190.8</v>
       </c>
     </row>
@@ -1369,12 +1249,15 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>510992.9</v>
+      </c>
+      <c r="C33" t="n">
         <v>1601164.4</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>1498017.5</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>1560266.3</v>
       </c>
     </row>
@@ -1385,12 +1268,15 @@
         </is>
       </c>
       <c r="B34" t="n">
+        <v>155030.6</v>
+      </c>
+      <c r="C34" t="n">
         <v>279981.9</v>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>338645.5</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>674535.2</v>
       </c>
     </row>
@@ -1400,14 +1286,24 @@
           <t>Улсын төсвийн хөрөнгөөр хайгуул хийсэн ордын нөхөн төлбөр</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="C35" t="n">
         <v>9693.799999999999</v>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>16328.4</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>16033.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Хайгуулын ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8953.5</v>
       </c>
     </row>
   </sheetData>

--- a/data.mn/public/datasets/mrpam-budget-revenue.xlsx
+++ b/data.mn/public/datasets/mrpam-budget-revenue.xlsx
@@ -10,10 +10,7 @@
     <sheet name="Data EN" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Өгөгдөл MN" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data EN'!$A$1:$F$421</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Өгөгдөл MN'!$A$1:$F$421</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,44 +414,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F421"/>
+  <dimension ref="A1:F427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>revenue_type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>plan_mln_mnt</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>actual_mln_mnt</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_of_plan</t>
         </is>
@@ -2371,8 +2364,6 @@
       <c r="D88" t="n">
         <v>277500</v>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2389,8 +2380,6 @@
       <c r="D89" t="n">
         <v>1740</v>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2517,8 +2506,6 @@
       <c r="D95" t="n">
         <v>277500</v>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2538,7 +2525,6 @@
       <c r="E96" t="n">
         <v>1144.3</v>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9690,8 +9676,139 @@
         <v>65.3</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B422" t="n">
+        <v>7</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Mineral licence fees</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>36605.2</v>
+      </c>
+      <c r="E422" t="n">
+        <v>24361.4</v>
+      </c>
+      <c r="F422" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B423" t="n">
+        <v>7</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Other revenue</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="E423" t="n">
+        <v>2044.6</v>
+      </c>
+      <c r="F423" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B424" t="n">
+        <v>7</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Petroleum exports</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>231472.9</v>
+      </c>
+      <c r="E424" t="n">
+        <v>125463.7</v>
+      </c>
+      <c r="F424" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B425" t="n">
+        <v>7</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Reimbursement for state-funded exploration</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>2395</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1456.5</v>
+      </c>
+      <c r="F425" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B426" t="n">
+        <v>7</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Tender revenue</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E426" t="n">
+        <v>73508.2</v>
+      </c>
+      <c r="F426" t="n">
+        <v>367.5</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B427" t="n">
+        <v>7</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>293986.9</v>
+      </c>
+      <c r="E427" t="n">
+        <v>226834.3</v>
+      </c>
+      <c r="F427" t="n">
+        <v>77.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F421"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9702,44 +9819,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F421"/>
+  <dimension ref="A1:F427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>он</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>сар</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>орлогын_төрөл</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>төлөвлөгөө_сая_төг</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>гүйцэтгэл_сая_төг</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>хувь</t>
         </is>
@@ -11652,8 +11769,6 @@
       <c r="D88" t="n">
         <v>277500</v>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11670,8 +11785,6 @@
       <c r="D89" t="n">
         <v>1740</v>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11798,8 +11911,6 @@
       <c r="D95" t="n">
         <v>277500</v>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11819,7 +11930,6 @@
       <c r="E96" t="n">
         <v>1144.3</v>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -18971,8 +19081,139 @@
         <v>65.3</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B422" t="n">
+        <v>7</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Ашигт малтмалын тусгай зөвшөөрлийн төлбөр</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>36605.2</v>
+      </c>
+      <c r="E422" t="n">
+        <v>24361.4</v>
+      </c>
+      <c r="F422" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B423" t="n">
+        <v>7</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Бусад орлого</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>3513.8</v>
+      </c>
+      <c r="E423" t="n">
+        <v>2044.6</v>
+      </c>
+      <c r="F423" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B424" t="n">
+        <v>7</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Газрын тосны экспорт</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>231472.9</v>
+      </c>
+      <c r="E424" t="n">
+        <v>125463.7</v>
+      </c>
+      <c r="F424" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B425" t="n">
+        <v>7</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Улсын төсвийн хөрөнгөөр хайгуул хийсэн ордын нөхөн төлбөр</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>2395</v>
+      </c>
+      <c r="E425" t="n">
+        <v>1456.5</v>
+      </c>
+      <c r="F425" t="n">
+        <v>60.8</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B426" t="n">
+        <v>7</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Сонгон шалгаруулалт</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E426" t="n">
+        <v>73508.2</v>
+      </c>
+      <c r="F426" t="n">
+        <v>367.5</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B427" t="n">
+        <v>7</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>БҮГД</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>293986.9</v>
+      </c>
+      <c r="E427" t="n">
+        <v>226834.3</v>
+      </c>
+      <c r="F427" t="n">
+        <v>77.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F421"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>